--- a/paper/figs/SCE_Tables.xlsx
+++ b/paper/figs/SCE_Tables.xlsx
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rainfed mortality, drawn twice per step</t>
+          <t>Rainfed mortality, drawn once per step</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paddy mortality, drawn twice per step</t>
+          <t>Paddy mortality, drawn once per step</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">

--- a/paper/figs/SCE_Tables.xlsx
+++ b/paper/figs/SCE_Tables.xlsx
@@ -729,11 +729,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15, 25, 35</t>
+          <t>12, 20, 28</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>239225</v>
+        <v>191380</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>239225</v>
+        <v>191380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2857,11 +2857,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15, 25, 35</t>
+          <t>12, 20, 28</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>paper/methods.md; config/config.yaml</t>
+          <t>paper/manuscript/methods.md; config/config.yaml</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/paper/figs/SCE_Tables.xlsx
+++ b/paper/figs/SCE_Tables.xlsx
@@ -3127,12 +3127,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>config/config.yaml; run_slurm.sh:67-68; data/*.tif via paper/build_tables.py</t>
+          <t>config/config.yaml; run_slurm_rerun.sh:150-151; data/*.tif via paper/build_tables.py</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>src/api/hunter.py, farmer.py, rice_farmer.py; config/config.yaml; run_slurm.sh:67-68</t>
+          <t>src/api/hunter.py, farmer.py, rice_farmer.py; config/config.yaml; run_slurm_rerun.sh:150-151</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>config/config.yaml; run_slurm.sh:67-68; provenance per paper/model-inventory.md section 4</t>
+          <t>config/config.yaml; run_slurm_rerun.sh:150-151; provenance per paper/model-inventory.md section 4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/paper/figs/SCE_Tables.xlsx
+++ b/paper/figs/SCE_Tables.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
